--- a/spectral_slope/TS9複合音単音.xlsx
+++ b/spectral_slope/TS9複合音単音.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Research\recording_application\spectral_slope\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{697BDA5B-9D97-438B-8DFC-190603230BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{580D51C2-3EA5-40A3-AFC4-13F0A03F9A1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13039,7 +13039,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AZ21"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="31.625" bestFit="1" customWidth="1"/>
@@ -17154,12 +17154,6 @@
         <v>-50.564510574368015</v>
       </c>
     </row>
-    <row r="21" spans="1:52" x14ac:dyDescent="0.15">
-      <c r="B21">
-        <f>MIN(B3:B20)</f>
-        <v>-3.330012258598801E-3</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
